--- a/croaker.xlsx
+++ b/croaker.xlsx
@@ -4,7 +4,8 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="products" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="config" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="cases" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="config" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>name</t>
   </si>
@@ -20,68 +21,107 @@
     <t>key</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>view_flg</t>
+  </si>
+  <si>
+    <t>簡易サージカル</t>
+  </si>
+  <si>
+    <t>treatment,purchase</t>
+  </si>
+  <si>
+    <t>リカバリーキット</t>
+  </si>
+  <si>
+    <t>ファーストエイド</t>
+  </si>
+  <si>
+    <t>メディキット</t>
+  </si>
+  <si>
+    <t>ターニケット</t>
+  </si>
+  <si>
+    <t>バンテージ</t>
+  </si>
+  <si>
+    <t>スプリント</t>
+  </si>
+  <si>
+    <t>treatment</t>
+  </si>
+  <si>
+    <t>点滴</t>
+  </si>
+  <si>
+    <t>氷のう</t>
+  </si>
+  <si>
+    <t>麻酔薬</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>メス</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>止血剤</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>鉗子</t>
+  </si>
+  <si>
+    <t>縫合針</t>
+  </si>
+  <si>
+    <t>治療</t>
+  </si>
+  <si>
+    <t>purchase</t>
+  </si>
+  <si>
+    <t>購入</t>
+  </si>
+  <si>
     <t>value</t>
   </si>
   <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>治療</t>
-  </si>
-  <si>
-    <t>簡易サージカル</t>
-  </si>
-  <si>
-    <t>購入</t>
-  </si>
-  <si>
-    <t>リカバリーキット</t>
-  </si>
-  <si>
-    <t>ファーストエイド</t>
-  </si>
-  <si>
-    <t>中型介入治療</t>
-  </si>
-  <si>
-    <t>メディキット</t>
-  </si>
-  <si>
-    <t>ターニケット</t>
-  </si>
-  <si>
-    <t>バンテージ</t>
-  </si>
-  <si>
-    <t>スプリント</t>
-  </si>
-  <si>
-    <t>点滴</t>
-  </si>
-  <si>
-    <t>氷のう</t>
-  </si>
-  <si>
-    <t>麻酔薬</t>
-  </si>
-  <si>
-    <t>メス</t>
-  </si>
-  <si>
-    <t>止血剤</t>
-  </si>
-  <si>
-    <t>鉗子</t>
-  </si>
-  <si>
-    <t>縫合針</t>
+    <t>title</t>
+  </si>
+  <si>
+    <t>闇医者お会計ツール</t>
+  </si>
+  <si>
+    <t>intervention_amount</t>
+  </si>
+  <si>
+    <t>intervention_case</t>
+  </si>
+  <si>
+    <t>intervention_label</t>
+  </si>
+  <si>
+    <t>中型介入</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -93,13 +133,30 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF232425"/>
+      <name val="&quot;Noto Sans SC&quot;"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F8F8"/>
+        <bgColor rgb="FFF8F8F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -108,18 +165,35 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -128,6 +202,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -337,6 +415,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="15.88"/>
+    <col customWidth="1" min="3" max="3" width="19.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -346,117 +425,162 @@
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1">
-        <v>10000.0</v>
+      <c r="B2" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1">
-        <v>10000.0</v>
+      <c r="B3" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1">
-        <v>10000.0</v>
+      <c r="B4" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1">
-        <v>10000.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="1">
-        <v>10000.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1">
-        <v>10000.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1">
-        <v>10000.0</v>
+      <c r="B8" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="1">
-        <v>10000.0</v>
+      <c r="B9" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="1">
-        <v>10000.0</v>
+      <c r="B10" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="1">
-        <v>10000.0</v>
+      <c r="B11" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="1">
-        <v>10000.0</v>
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="1">
-        <v>10000.0</v>
+      <c r="A13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="1">
-        <v>10000.0</v>
+      <c r="A14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="1">
-        <v>10000.0</v>
+      <c r="A15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="2">
+        <v>10000.0</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -472,35 +596,106 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:D3">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(A1))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="17.63"/>
+    <col customWidth="1" min="2" max="2" width="16.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
+      <c r="B1" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.7</v>
+      <c r="A2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0.9</v>
+      <c r="A3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1500000.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1500000.0</v>
+      <c r="A4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
